--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487099_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487099_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4585</v>
+        <v>3.3117</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3929</v>
+        <v>2.1926</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0656</v>
+        <v>1.1191</v>
       </c>
       <c r="G2" t="n">
         <v>2.1166</v>
@@ -610,13 +610,13 @@
         <v>1.158</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1838</v>
+        <v>0.037</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3437</v>
+        <v>-0.544</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5274</v>
+        <v>0.581</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0527</v>
+        <v>3.0061</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2469</v>
+        <v>4.1468</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1942</v>
+        <v>-1.1406</v>
       </c>
       <c r="G3" t="n">
         <v>2.7772</v>
@@ -688,13 +688,13 @@
         <v>0.965</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1877</v>
+        <v>-0.2343</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5816</v>
+        <v>-0.6818</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3939</v>
+        <v>0.4475</v>
       </c>
       <c r="V3" t="n">
         <v>0.6562</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. DIAGNE</t>
+          <t>F. RODRIGUEZ HERRON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1517</v>
+        <v>0.7993</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6948</v>
+        <v>1.1634</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4569</v>
+        <v>-0.3641</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.7338</v>
+        <v>1.9214</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.8569</v>
+        <v>1.8122</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8768</v>
+        <v>0.1092</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.3582</v>
+        <v>2.0212</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.2942</v>
+        <v>1.8991</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9361</v>
+        <v>0.1221</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.3756</v>
+        <v>-0.0998</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5627</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.8129</v>
+        <v>-0.0129</v>
       </c>
       <c r="P4" t="n">
-        <v>0.965</v>
+        <v>0.386</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.158</v>
+        <v>-0.193</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1231</v>
+        <v>0.579</v>
       </c>
       <c r="S4" t="n">
-        <v>4.9204</v>
+        <v>0.0479</v>
       </c>
       <c r="T4" t="n">
-        <v>1.983</v>
+        <v>-0.2945</v>
       </c>
       <c r="U4" t="n">
-        <v>2.9373</v>
+        <v>0.3424</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.5561</v>
       </c>
       <c r="W4" t="n">
-        <v>1.228</v>
+        <v>-0.3704</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.228</v>
+        <v>-1.1857</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. RODRIGUEZ HERRON</t>
+          <t>L. SANCHEZ TURRION</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3918</v>
+        <v>-0.2281</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8629</v>
+        <v>-0.8028</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4711</v>
+        <v>0.5747</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9214</v>
+        <v>-1.1187</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8122</v>
+        <v>-0.7524</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1092</v>
+        <v>-0.3663</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0212</v>
+        <v>-0.5648</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8991</v>
+        <v>-0.6055</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1221</v>
+        <v>0.0407</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0998</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.1469</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0129</v>
+        <v>-0.407</v>
       </c>
       <c r="P5" t="n">
-        <v>0.386</v>
+        <v>0.965</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.193</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.579</v>
+        <v>0.965</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3596</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5949</v>
+        <v>-0.238</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2353</v>
+        <v>0.1636</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.5561</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3704</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. SANCHEZ TURRION</t>
+          <t>L. BLANCO DE LA CRUZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1478</v>
+        <v>-1.2255</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8028</v>
+        <v>-1.3378</v>
       </c>
       <c r="F6" t="n">
-        <v>0.655</v>
+        <v>0.1123</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.1187</v>
+        <v>-0.4677</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7524</v>
+        <v>0.3592</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3663</v>
+        <v>-0.8268</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5648</v>
+        <v>0.7866</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6055</v>
+        <v>0.7866</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0407</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-1.2542</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1469</v>
+        <v>-0.4274</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.407</v>
+        <v>-0.8268</v>
       </c>
       <c r="P6" t="n">
-        <v>0.965</v>
+        <v>-0.965</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R6" t="n">
         <v>0.965</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0059</v>
+        <v>0.2072</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.238</v>
+        <v>-0.1943</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2439</v>
+        <v>0.4015</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. BLANCO DE LA CRUZ</t>
+          <t>M. DIAGNE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.867</v>
+        <v>-1.2362</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7384</v>
+        <v>-0.4082</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1286</v>
+        <v>-0.8280999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4677</v>
+        <v>-3.7338</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3592</v>
+        <v>-2.8569</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8268</v>
+        <v>-0.8768</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7866</v>
+        <v>-0.3582</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7866</v>
+        <v>-1.2942</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.9361</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2542</v>
+        <v>-3.3756</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4274</v>
+        <v>-1.5627</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8268</v>
+        <v>-1.8129</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.965</v>
+        <v>0.965</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9301</v>
+        <v>-1.158</v>
       </c>
       <c r="R7" t="n">
-        <v>0.965</v>
+        <v>2.1231</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4343</v>
+        <v>1.5325</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5949</v>
+        <v>-0.1199</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1606</v>
+        <v>1.6524</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.5657</v>
+        <v>-3.1116</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.8021</v>
+        <v>-2.4015</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7635999999999999</v>
+        <v>-0.7101</v>
       </c>
       <c r="G8" t="n">
         <v>-3.1705</v>
@@ -1078,13 +1078,13 @@
         <v>0.965</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3953</v>
+        <v>0.0588</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5949</v>
+        <v>-0.1943</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1996</v>
+        <v>0.2531</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ALLAS MENESES</t>
+          <t>M. HERRERO CRESPO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.3254</v>
+        <v>-4.4825</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.472</v>
+        <v>-1.4257</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8532999999999999</v>
+        <v>-3.0568</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.3053</v>
+        <v>-0.9874000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.9736</v>
+        <v>0.6405</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3316</v>
+        <v>-1.628</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.0977</v>
+        <v>1.7345</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.9252</v>
+        <v>1.7023</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1724</v>
+        <v>0.0321</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2076</v>
+        <v>-2.7219</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0484</v>
+        <v>-1.0618</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1592</v>
+        <v>-1.6601</v>
       </c>
       <c r="P9" t="n">
-        <v>0.386</v>
+        <v>-1.158</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.0881</v>
       </c>
       <c r="R9" t="n">
-        <v>0.386</v>
+        <v>1.9301</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.078</v>
+        <v>-0.2092</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0462</v>
+        <v>-0.6861</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0317</v>
+        <v>0.4769</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3281</v>
+        <v>-2.1278</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3281</v>
+        <v>0.614</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.7418</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. HERRERO CRESPO</t>
+          <t>A. ALLAS MENESES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.6316</v>
+        <v>-4.5187</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2268</v>
+        <v>-3.7724</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.4048</v>
+        <v>-0.7463</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9874000000000001</v>
+        <v>-4.3053</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6405</v>
+        <v>-2.9736</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.628</v>
+        <v>-1.3316</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7345</v>
+        <v>-3.0977</v>
       </c>
       <c r="K10" t="n">
-        <v>1.7023</v>
+        <v>-1.9252</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0321</v>
+        <v>-1.1724</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.7219</v>
+        <v>-1.2076</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0618</v>
+        <v>-1.0484</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6601</v>
+        <v>-0.1592</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.158</v>
+        <v>0.386</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0881</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9301</v>
+        <v>0.386</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3583</v>
+        <v>-0.2713</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.4872</v>
+        <v>-0.3467</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1289</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1278</v>
+        <v>-0.3281</v>
       </c>
       <c r="W10" t="n">
-        <v>0.614</v>
+        <v>-0.3281</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.7418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.140700000000001</v>
+        <v>-6.938</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.1913</v>
+        <v>-4.3902</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9494</v>
+        <v>-2.5478</v>
       </c>
       <c r="G11" t="n">
         <v>-5.6437</v>
@@ -1312,13 +1312,13 @@
         <v>2.5091</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.0061</v>
+        <v>-0.8034</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.9036</v>
+        <v>-1.1025</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1025</v>
+        <v>0.2991</v>
       </c>
       <c r="V11" t="n">
         <v>-1.842</v>
@@ -1348,16 +1348,16 @@
         <v>-14.6235</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.035900000000001</v>
+        <v>-7.035800000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.587499999999999</v>
+        <v>-7.5877</v>
       </c>
       <c r="G12" t="n">
         <v>-12.6119</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.471799999999999</v>
+        <v>-4.4718</v>
       </c>
       <c r="I12" t="n">
         <v>-8.139700000000001</v>
@@ -1390,13 +1390,13 @@
         <v>12.5453</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2907999999999999</v>
+        <v>0.2907999999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.402</v>
+        <v>-4.4021</v>
       </c>
       <c r="U12" t="n">
-        <v>4.692699999999999</v>
+        <v>4.692800000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-5.197800000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.3153</v>
+        <v>10.7694</v>
       </c>
       <c r="E13" t="n">
-        <v>8.357200000000001</v>
+        <v>8.7578</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9581</v>
+        <v>2.0117</v>
       </c>
       <c r="G13" t="n">
         <v>7.3592</v>
@@ -1468,13 +1468,13 @@
         <v>1.7371</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.928</v>
+        <v>-0.4739</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.5467</v>
+        <v>-1.1461</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6186</v>
+        <v>0.6722</v>
       </c>
       <c r="V13" t="n">
         <v>3.1122</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.7858</v>
+        <v>6.8463</v>
       </c>
       <c r="E14" t="n">
-        <v>5.228</v>
+        <v>5.1278</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5579</v>
+        <v>1.7185</v>
       </c>
       <c r="G14" t="n">
         <v>4.5029</v>
@@ -1546,13 +1546,13 @@
         <v>1.5441</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2935</v>
+        <v>-0.233</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8196</v>
+        <v>-0.9197</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5261</v>
+        <v>0.6867</v>
       </c>
       <c r="V14" t="n">
         <v>3.9275</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. CAMPBELL</t>
+          <t>A. FRECHILLA GOMEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2876</v>
+        <v>1.1699</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8759</v>
+        <v>-0.9654</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4117</v>
+        <v>2.1352</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2363</v>
+        <v>2.6462</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5647</v>
+        <v>0.497</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3285</v>
+        <v>2.1492</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1962</v>
+        <v>2.6522</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8056</v>
+        <v>1.1385</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3906</v>
+        <v>1.5137</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9599</v>
+        <v>-0.006</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2409</v>
+        <v>-0.6415</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.719</v>
+        <v>0.6355</v>
       </c>
       <c r="P15" t="n">
-        <v>0.386</v>
+        <v>-1.158</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3511</v>
+        <v>1.7371</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6074000000000001</v>
+        <v>-0.3183</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6411</v>
+        <v>-0.7224</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2486</v>
+        <v>0.4042</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9421</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. FRECHILLA GOMEZ</t>
+          <t>S. CAMPBELL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0221</v>
+        <v>0.893</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7651</v>
+        <v>0.7758</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7872</v>
+        <v>0.1172</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6462</v>
+        <v>1.2363</v>
       </c>
       <c r="H16" t="n">
-        <v>0.497</v>
+        <v>1.5647</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1492</v>
+        <v>-0.3285</v>
       </c>
       <c r="J16" t="n">
-        <v>2.6522</v>
+        <v>2.1962</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1385</v>
+        <v>1.8056</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5137</v>
+        <v>0.3906</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.006</v>
+        <v>-0.9599</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6415</v>
+        <v>-0.2409</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6355</v>
+        <v>-0.719</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.158</v>
+        <v>0.386</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7371</v>
+        <v>1.3511</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.466</v>
+        <v>0.2128</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5221</v>
+        <v>-0.7413</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0562</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.9421</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. MENDEZ MADERA</t>
+          <t>N. KIAMESO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.666</v>
+        <v>0.5786</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5712</v>
+        <v>-0.7459</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0948</v>
+        <v>1.3245</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0713</v>
+        <v>-0.1335</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1615</v>
+        <v>0.4006</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2328</v>
+        <v>-0.5341</v>
       </c>
       <c r="J17" t="n">
-        <v>0.08210000000000001</v>
+        <v>-0.6676</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0414</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0407</v>
+        <v>-0.6676</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1534</v>
+        <v>0.5341</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1201</v>
+        <v>0.4006</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2735</v>
+        <v>0.1335</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.193</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.193</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4092</v>
+        <v>-0.1372</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4891</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.08</v>
+        <v>-0.0588</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3281</v>
+        <v>0.6562</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3281</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. KIAMESO</t>
+          <t>M. MENDEZ MADERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.532</v>
+        <v>0.3457</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8461</v>
+        <v>0.1707</v>
       </c>
       <c r="F18" t="n">
-        <v>1.378</v>
+        <v>0.1751</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1335</v>
+        <v>-0.0713</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4006</v>
+        <v>0.1615</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5341</v>
+        <v>-0.2328</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6676</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.0414</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6676</v>
+        <v>0.0407</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5341</v>
+        <v>-0.1534</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4006</v>
+        <v>0.1201</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1335</v>
+        <v>-0.2735</v>
       </c>
       <c r="P18" t="n">
-        <v>0.193</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.193</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1838</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1785</v>
+        <v>0.0886</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0053</v>
+        <v>0.0003</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6562</v>
+        <v>0.3281</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6562</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7302999999999999</v>
+        <v>0.0718</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1315</v>
+        <v>0.5321</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8618</v>
+        <v>-0.4602</v>
       </c>
       <c r="G19" t="n">
         <v>-0.7151</v>
@@ -1936,13 +1936,13 @@
         <v>0.772</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7872</v>
+        <v>0.0149</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6544</v>
+        <v>-0.2538</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1329</v>
+        <v>0.2687</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.053</v>
+        <v>-0.7923</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1892</v>
+        <v>0.2893</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2422</v>
+        <v>-1.0816</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8236</v>
@@ -2014,13 +2014,13 @@
         <v>0.386</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2644</v>
+        <v>-0.0036</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.238</v>
+        <v>-0.1378</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0264</v>
+        <v>0.1342</v>
       </c>
       <c r="V20" t="n">
         <v>0.614</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.2022</v>
+        <v>-5.2591</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.5403</v>
+        <v>-5.7406</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3381</v>
+        <v>0.4815</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3893</v>
@@ -2092,13 +2092,13 @@
         <v>1.9301</v>
       </c>
       <c r="S21" t="n">
-        <v>1.6154</v>
+        <v>0.5585</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5816</v>
+        <v>-0.7819</v>
       </c>
       <c r="U21" t="n">
-        <v>2.1971</v>
+        <v>1.3404</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4982</v>
@@ -2128,10 +2128,10 @@
         <v>14.6233</v>
       </c>
       <c r="E22" t="n">
-        <v>8.201499999999999</v>
+        <v>8.201599999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>6.4218</v>
+        <v>6.4219</v>
       </c>
       <c r="G22" t="n">
         <v>12.6118</v>
@@ -2170,13 +2170,13 @@
         <v>9.650500000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2909000000000002</v>
+        <v>-0.2908999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-4.6929</v>
+        <v>-4.692699999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>4.401999999999999</v>
+        <v>4.402</v>
       </c>
       <c r="V22" t="n">
         <v>5.197699999999999</v>
